--- a/public/templates/refrigerants-template.xlsx
+++ b/public/templates/refrigerants-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthika Suresh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Hackathon\ESGroww\ESGroww\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{874122F9-D4A2-4F9D-BE90-381E2A16ACF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A0E322-4D05-4284-B81B-9F010ABCAADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AB489A9B-DEC6-4649-A229-0154296AA7BB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{AB489A9B-DEC6-4649-A229-0154296AA7BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,25 +34,34 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>refrigerantType</t>
   </si>
   <si>
     <t>refrigerantLeakKg</t>
+  </si>
+  <si>
+    <t>❄️  Refrigerant Leakage Upload Template</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>4-digit calendar year of the leakage / recharge event.</t>
+  </si>
+  <si>
+    <t>Type / grade of refrigerant. Common values: R-22, R-410A, R-32, R-134a, R-407C.</t>
+  </si>
+  <si>
+    <t>Total quantity of refrigerant leaked or recharged during the year, in kg. Based on maintenance records.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,22 +71,56 @@
     </font>
     <font>
       <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF1A5276"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A5276"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF117A65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF5FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -85,13 +128,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -408,24 +475,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDDB5C36-45E1-4B1B-94E0-ADBBA689652C}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.36328125" customWidth="1"/>
+    <col min="2" max="2" width="22.90625" customWidth="1"/>
+    <col min="3" max="3" width="28.08984375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+    </row>
+    <row r="3" spans="1:3" ht="48" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/templates/refrigerants-template.xlsx
+++ b/public/templates/refrigerants-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Hackathon\ESGroww\ESGroww\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A0E322-4D05-4284-B81B-9F010ABCAADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1543D90E-802B-41E9-A6DE-CF466EDC64B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{AB489A9B-DEC6-4649-A229-0154296AA7BB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>refrigerantType</t>
   </si>
@@ -55,13 +55,19 @@
   </si>
   <si>
     <t>Total quantity of refrigerant leaked or recharged during the year, in kg. Based on maintenance records.</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>Month of data entry. Enter as number (1–12) or text (Jan–Dec / January–December).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,12 +79,6 @@
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -120,7 +120,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -143,23 +143,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -475,46 +484,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDDB5C36-45E1-4B1B-94E0-ADBBA689652C}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.36328125" customWidth="1"/>
-    <col min="2" max="2" width="22.90625" customWidth="1"/>
-    <col min="3" max="3" width="28.08984375" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" customWidth="1"/>
+    <col min="3" max="3" width="22.90625" customWidth="1"/>
+    <col min="4" max="4" width="28.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="48" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:4" ht="72" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
